--- a/productSource/products.xlsx
+++ b/productSource/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,45 +439,55 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Vehicle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ShareClass</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ExposureCurrency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ProductCost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FeeGroup</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>DistributionYield</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>MinimumInvestment</t>
         </is>
@@ -502,41 +512,51 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.25</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>3.2</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -559,41 +579,51 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.28</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>4.8</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -616,41 +646,51 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.22</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>4.7</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -677,41 +717,51 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.42</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>4.8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -738,41 +788,51 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.55</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>4.8</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -799,41 +859,51 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.38</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>4.7</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -860,38 +930,48 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.14</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -918,38 +998,48 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.12</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -976,41 +1066,51 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.46</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>4.5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1037,41 +1137,51 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.72</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>6.9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1098,41 +1208,51 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.85</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>6.3</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1159,41 +1279,51 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.79</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>5.4</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1220,41 +1350,51 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.91</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>6.3</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1281,38 +1421,48 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.34</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -1339,38 +1489,48 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.39</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>6.3</v>
       </c>
     </row>
@@ -1397,38 +1557,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.09</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1455,41 +1625,51 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.71</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>1.1</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1516,41 +1696,51 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.68</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>2.7</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1577,41 +1767,51 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>1.12</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>2.4</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1638,38 +1838,48 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.25</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -1696,38 +1906,48 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.37</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -1750,41 +1970,51 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.55</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -1807,41 +2037,51 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.55</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>1.3</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -1868,41 +2108,51 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>2.7</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1925,41 +2175,51 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>1.35</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -1982,41 +2242,51 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>1.48</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2039,41 +2309,51 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>1.62</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2096,41 +2376,51 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>1.55</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2157,41 +2447,51 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.96</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -2218,41 +2518,51 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>1.08</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -2275,41 +2585,51 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>1.25</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2332,41 +2652,51 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>1.45</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2389,41 +2719,51 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>1.5</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2446,41 +2786,51 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>1.1</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2503,41 +2853,51 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>1.72</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2560,41 +2920,51 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>1.3</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>3.8</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2617,41 +2987,51 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>1.4</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2674,41 +3054,51 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>1.35</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>8.6</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2731,41 +3121,51 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>1.22</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>4.1</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2788,41 +3188,51 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>1.38</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>2.9</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -2849,41 +3259,51 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Asset Allocation Strategies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.85</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -2910,41 +3330,51 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hybrid Fixed Income</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>0.65</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>2.2</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -2971,41 +3401,51 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.44</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>4.8</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3032,38 +3472,48 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.16</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -3090,41 +3540,51 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.48</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>4.2</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3151,41 +3611,51 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.62</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>4.3</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3212,41 +3682,51 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.76</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>6.9</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3273,41 +3753,51 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.89</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>6.3</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3334,38 +3824,48 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.14</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -3392,41 +3892,51 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.72</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>2.7</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3453,41 +3963,51 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>1.05</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>2.4</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3514,41 +4034,51 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.88</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>0.8</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3575,41 +4105,51 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.79</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>2.7</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3632,41 +4172,51 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>1.38</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -3689,41 +4239,51 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>1.55</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>0</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -3746,41 +4306,51 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>1.32</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>3.8</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -3807,41 +4377,51 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Asset Allocation Strategies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.88</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3864,41 +4444,51 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.52</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>4.8</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -3921,41 +4511,51 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>0.54</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>4.8</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -3978,41 +4578,51 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Investment Grade Fixed Income</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>0.4</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>4.7</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4035,41 +4645,51 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H62" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>0.18</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>4.5</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4092,41 +4712,51 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>0.15</v>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>4.9</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4149,41 +4779,51 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>6.9</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4206,41 +4846,51 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other Fixed Income</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>6.3</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4263,41 +4913,51 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>0.2</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>2.1</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4320,41 +4980,51 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H67" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>0.78</v>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>3</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4377,41 +5047,51 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Public Equity</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>1.08</v>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>2.4</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4434,41 +5114,51 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Public Equity</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>0.32</v>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>2.4</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4491,41 +5181,51 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H70" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>1.12</v>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>0</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4548,41 +5248,51 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>1.24</v>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>0</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -4605,41 +5315,51 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>ICAV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
+          <t>Accumulating</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>1.58</v>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>0</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -4662,41 +5382,51 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>ICAV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H73" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>1.48</v>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -4719,41 +5449,51 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Asset Allocation Strategies</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>UCITS</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
       <c r="H74" t="inlineStr">
         <is>
+          <t>Distributing</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>0.92</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>10000</v>
       </c>
     </row>
